--- a/public/assets/Products.xlsx
+++ b/public/assets/Products.xlsx
@@ -1,52 +1,108 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商品导入模板" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet sheetId="1" name="Products" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <si>
+    <t>商品名称</t>
+  </si>
+  <si>
+    <t>分类名称</t>
+  </si>
+  <si>
+    <t>是否支持定制</t>
+  </si>
+  <si>
+    <t>商品评分</t>
+  </si>
+  <si>
+    <t>售价</t>
+  </si>
+  <si>
+    <t>原价</t>
+  </si>
+  <si>
+    <t>库存</t>
+  </si>
+  <si>
+    <t>单位（件/盒）</t>
+  </si>
+  <si>
+    <t>生产厂家</t>
+  </si>
+  <si>
+    <t>品牌</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>图片文件夹名称</t>
+  </si>
+  <si>
+    <t>示例商品</t>
+  </si>
+  <si>
+    <t>分类A</t>
+  </si>
+  <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>件</t>
+  </si>
+  <si>
+    <t>示例厂家</t>
+  </si>
+  <si>
+    <t>示例品牌</t>
+  </si>
+  <si>
+    <t>示例描述</t>
+  </si>
+  <si>
+    <t>product01</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <b/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="87CEEB"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -54,182 +110,30 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00B7B7B7"/>
-      </left>
-      <right style="thin">
-        <color rgb="00B7B7B7"/>
-      </right>
-      <top style="thin">
-        <color rgb="00B7B7B7"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00B7B7B7"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>系统</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>唯一编号，用于前台/后台/表格中标识商品。
-留空则系统自动生成。
-如填写需保证唯一，不能与已有商品重复。</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>必填，最多200字。</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>必填，需与系统中已存在的分类名称完全一致（否则整行判定失败，不会自动创建分类）。</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>必填，数字，不能为负数，即销售价。</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>选填，数字。若填写，原价不能低于价格；原价高于价格时前端将显示优惠标识。</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>必填，非负整数。</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>选填，如：件、盒、套。</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>选填。</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>选填。</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>填写“是”或“否”，留空默认视为“否”。
-填“是”时，商品详情页会显示“支持定制”标识。</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t>填写数字，范围 0～5，支持半颗星，如 4 表示4星，4.5表示4星半。
-留空默认按5分处理。</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t>选填，商品简要描述文字。</t>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
-      <text>
-        <t>必填。需与随 Excel 一同上传的 images.zip 压缩包中的图片文件夹名称一致，系统会自动匹配该文件夹内的图片作为商品图片。</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -307,6 +211,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -341,6 +246,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -375,20 +281,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -510,109 +412,145 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="28" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>商品编号(SKU)</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>商品名称</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>分类名称</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>价格</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>原价</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>库存</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>单位（件/盒）</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>生产厂家</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>品牌</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>是否支持定制</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>商品评分</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>描述</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>图片文件夹名称</t>
-        </is>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>1999</v>
+      </c>
+      <c r="F2">
+        <v>2499</v>
+      </c>
+      <c r="G2">
+        <v>100</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="输入不合法" error="请选择&quot;是&quot;或&quot;否&quot;" promptTitle="是否支持定制" prompt="请点击单元格右侧箭头选择：是 / 否" type="list">
-      <formula1>"是,否"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>